--- a/data/trans_orig/P16A20_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P16A20_2023-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha consumido medicamentos para la alteración del tiroides en 2007</t>
+          <t>Población según si ha consumido medicamentos para la alteración del tiroides en 2007 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1966</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2095</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>163014</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>164980</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>105017</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>107112</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>270068</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>272092</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1921</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>302822</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>304847</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>207304</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>209225</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>512086</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>514072</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1890</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1963</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>202180</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>204179</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>127237</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>129127</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>331344</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>333307</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1941</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1836</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1902</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>213568</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>215509</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>155114</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>156950</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>370556</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>372458</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1923</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1969</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>105419</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>107342</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>74097</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>76066</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>181453</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>183408</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1984</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1945</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1979</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>159393</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>161377</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>96477</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>98422</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>257820</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>259799</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>374814</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>376823</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>280975</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>282979</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>657791</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>659802</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>410643</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>412604</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>337852</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>339841</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>750468</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>752445</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1969</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1945671</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1947662</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1397753</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1399722</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3345402</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3347384</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,94%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha consumido medicamentos para la alteración del tiroides en 2012</t>
+          <t>Población según si ha consumido medicamentos para la alteración del tiroides en 2012 (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2161</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>124251</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>126219</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>62208</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>64369</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>188546</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>190589</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1987</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>246488</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>248475</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>145538</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>147559</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>394028</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>396034</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1869</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2051</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1939</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>147190</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>149059</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>79325</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>81376</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>228496</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>230435</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>189102</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>191128</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>97071</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>99069</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>288173</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>290198</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1874</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>97121</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>99164</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>39326</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>41200</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>138355</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>140364</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1979</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1923</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1973</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>110536</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>112515</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>59376</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>61299</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>171841</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>173814</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2069</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2047</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>314184</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>316207</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>222210</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>224279</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>538439</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>540486</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2041</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2082</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2062</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>451962</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>454003</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>337404</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>339486</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>791427</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>793489</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2064</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1694758</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1696771</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,88%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1056573</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1058637</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2753375</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2755408</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha consumido medicamentos para la alteración del tiroides en 2016</t>
+          <t>Población según si ha consumido medicamentos para la alteración del tiroides en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2142</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1939</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2064</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>118524</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>120666</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>86116</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>88055</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>206657</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>208721</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1981</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>258060</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>260081</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>170498</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>172479</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>430549</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>432560</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1821</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1836</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1835</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>155769</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>157590</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>113091</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>114927</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>270682</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>272517</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1909</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1983</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>142163</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>144181</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>96701</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>98610</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>240809</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>242792</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1885</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1796</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1860</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>118059</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>119944</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>75067</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>76863</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>194947</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>196807</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1857</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1923</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>139774</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>141729</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>97949</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>99806</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>239613</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>241536</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2176</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1958</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>356030</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>358206</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>295959</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>297917</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>654048</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>656123</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>399948</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>401963</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>295266</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>297268</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>697219</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>699232</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2032</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1702330</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1704362</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,88%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1243977</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1245925</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2948290</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2950287</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha consumido medicamentos para la alteración del tiroides en 2023</t>
+          <t>Población según si ha consumido medicamentos para la alteración del tiroides en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1757</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11550</t>
+          <t>11340</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14035</t>
+          <t>13719</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28492</t>
+          <t>27987</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17796</t>
+          <t>17675</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33534</t>
+          <t>34998</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>299893</t>
+          <t>300103</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>309616</t>
+          <t>309686</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>261143</t>
+          <t>261648</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>275600</t>
+          <t>275916</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>567543</t>
+          <t>566079</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>583281</t>
+          <t>583402</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,06%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2227</t>
+          <t>1774</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13007</t>
+          <t>12913</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22989</t>
+          <t>23656</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43598</t>
+          <t>45092</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27349</t>
+          <t>26366</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>50187</t>
+          <t>48947</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>504386</t>
+          <t>504480</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>515166</t>
+          <t>515619</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>470127</t>
+          <t>468633</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>490736</t>
+          <t>490069</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>980931</t>
+          <t>982171</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1003769</t>
+          <t>1004752</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,44%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1573</t>
+          <t>1866</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9332</t>
+          <t>9130</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18753</t>
+          <t>19128</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34445</t>
+          <t>34588</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22426</t>
+          <t>22552</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>41110</t>
+          <t>40564</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,1%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>306718</t>
+          <t>306920</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>314477</t>
+          <t>314184</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>314683</t>
+          <t>314540</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>330375</t>
+          <t>330000</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>624068</t>
+          <t>624614</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>642752</t>
+          <t>642626</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,61%</t>
         </is>
       </c>
     </row>
@@ -11736,7 +11736,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3650</t>
+          <t>3512</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11751,7 +11751,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17718</t>
+          <t>18711</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41976</t>
+          <t>43670</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21939</t>
+          <t>21965</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>42797</t>
+          <t>43900</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -11844,7 +11844,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>308907</t>
+          <t>309045</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>433742</t>
+          <t>432048</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>458000</t>
+          <t>457007</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>745477</t>
+          <t>744374</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>766335</t>
+          <t>766309</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,21%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1317</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12297</t>
+          <t>11570</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13593</t>
+          <t>13896</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24194</t>
+          <t>24471</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16995</t>
+          <t>16884</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31428</t>
+          <t>31258</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,08%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>166445</t>
+          <t>167172</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>177470</t>
+          <t>177425</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>184105</t>
+          <t>183828</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>194706</t>
+          <t>194403</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>355613</t>
+          <t>355783</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>370046</t>
+          <t>370157</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,64%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>775</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6037</t>
+          <t>5636</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19350</t>
+          <t>20013</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>33393</t>
+          <t>33605</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>22279</t>
+          <t>21878</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>37039</t>
+          <t>36566</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,94%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>263599</t>
+          <t>264000</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>269152</t>
+          <t>268861</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>223663</t>
+          <t>223451</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>237706</t>
+          <t>237043</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>489653</t>
+          <t>490126</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>504413</t>
+          <t>504814</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,85%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6172</t>
+          <t>5838</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26497</t>
+          <t>27722</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>95298</t>
+          <t>91829</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>566469</t>
+          <t>566868</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>66,75%</t>
+          <t>66,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>94573</t>
+          <t>95265</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>716659</t>
+          <t>650464</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>44,16%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>597782</t>
+          <t>596557</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>618107</t>
+          <t>618441</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>282149</t>
+          <t>281750</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>753320</t>
+          <t>756789</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>756238</t>
+          <t>822433</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1378324</t>
+          <t>1377632</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>55,84%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,53%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>3158</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>17932</t>
+          <t>18500</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>42842</t>
+          <t>43570</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>72522</t>
+          <t>75828</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>41011</t>
+          <t>39318</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>85123</t>
+          <t>86310</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>910788</t>
+          <t>910220</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>924849</t>
+          <t>925562</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>642329</t>
+          <t>639023</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>672009</t>
+          <t>671281</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1558449</t>
+          <t>1557262</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1602561</t>
+          <t>1604254</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,61%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>30900</t>
+          <t>31327</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>62529</t>
+          <t>61801</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>288444</t>
+          <t>287815</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1032918</t>
+          <t>1179965</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>323603</t>
+          <t>322547</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1233134</t>
+          <t>1247335</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,53%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3396291</t>
+          <t>3397019</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3427920</t>
+          <t>3427493</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2624110</t>
+          <t>2477063</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3368584</t>
+          <t>3369213</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>71,76%</t>
+          <t>67,73%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5882714</t>
+          <t>5868513</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6792245</t>
+          <t>6793301</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,47%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A20_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P16A20_2023-Provincia-trans_orig.xlsx
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4963</t>
+          <t>4452</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1757</t>
+          <t>1647</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11340</t>
+          <t>9950</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>19378</t>
+          <t>19761</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13719</t>
+          <t>13888</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27987</t>
+          <t>27484</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>24341</t>
+          <t>24213</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17675</t>
+          <t>17505</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34998</t>
+          <t>32968</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>306480</t>
+          <t>314393</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>300103</t>
+          <t>308895</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>309686</t>
+          <t>317198</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>270257</t>
+          <t>296300</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>261648</t>
+          <t>288577</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>275916</t>
+          <t>302173</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>576736</t>
+          <t>610693</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>566079</t>
+          <t>601938</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>583402</t>
+          <t>617401</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,24%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>5646</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1774</t>
+          <t>1868</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12913</t>
+          <t>11673</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>32218</t>
+          <t>32604</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23656</t>
+          <t>23771</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45092</t>
+          <t>43312</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>37656</t>
+          <t>38251</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26366</t>
+          <t>28263</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>48947</t>
+          <t>52910</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>511954</t>
+          <t>524014</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>504480</t>
+          <t>517987</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>515619</t>
+          <t>527792</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>481507</t>
+          <t>512609</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>468633</t>
+          <t>501901</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>490069</t>
+          <t>521442</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>993462</t>
+          <t>1036622</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>982171</t>
+          <t>1021963</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1004752</t>
+          <t>1046610</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,37%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>513725</t>
+          <t>545213</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>513725</t>
+          <t>545213</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>513725</t>
+          <t>545213</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1031118</t>
+          <t>1074873</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1031118</t>
+          <t>1074873</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1031118</t>
+          <t>1074873</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>4497</t>
+          <t>4399</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1866</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9130</t>
+          <t>9509</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>25819</t>
+          <t>26040</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19128</t>
+          <t>19657</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34588</t>
+          <t>34771</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>30316</t>
+          <t>30439</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22552</t>
+          <t>23681</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>40564</t>
+          <t>41077</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>311553</t>
+          <t>311594</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>306920</t>
+          <t>306484</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>314184</t>
+          <t>314394</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>323309</t>
+          <t>330341</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>314540</t>
+          <t>321610</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>330000</t>
+          <t>336724</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>634862</t>
+          <t>641936</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>624614</t>
+          <t>631298</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>642626</t>
+          <t>648694</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,48%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,7 +11726,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1165</t>
+          <t>1175</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -11736,12 +11736,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3512</t>
+          <t>4120</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -11751,7 +11751,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>30681</t>
+          <t>32886</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18711</t>
+          <t>24226</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43670</t>
+          <t>42733</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>31846</t>
+          <t>34061</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21965</t>
+          <t>25329</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>43900</t>
+          <t>44756</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -11839,27 +11839,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>311392</t>
+          <t>371970</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>309045</t>
+          <t>369025</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>445037</t>
+          <t>389075</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>432048</t>
+          <t>379228</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>457007</t>
+          <t>397735</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>756428</t>
+          <t>761046</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>744374</t>
+          <t>750351</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>766309</t>
+          <t>769778</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>96,81%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>4495</t>
+          <t>4477</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1317</t>
+          <t>751</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11570</t>
+          <t>11811</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>18432</t>
+          <t>19718</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13896</t>
+          <t>14936</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24471</t>
+          <t>26379</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>22927</t>
+          <t>24195</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16884</t>
+          <t>18045</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31258</t>
+          <t>32298</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,47%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>174247</t>
+          <t>201188</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>167172</t>
+          <t>193854</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>177425</t>
+          <t>204914</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>189867</t>
+          <t>207118</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>183828</t>
+          <t>200457</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>194403</t>
+          <t>211900</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>364114</t>
+          <t>408306</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>355783</t>
+          <t>400203</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>370157</t>
+          <t>414456</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,83%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>208299</t>
+          <t>226836</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>208299</t>
+          <t>226836</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208299</t>
+          <t>226836</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>387041</t>
+          <t>432501</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>387041</t>
+          <t>432501</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>387041</t>
+          <t>432501</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>2069</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>775</t>
+          <t>509</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5636</t>
+          <t>5606</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,27 +12447,27 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>26108</t>
+          <t>26987</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20013</t>
+          <t>19972</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>33605</t>
+          <t>34470</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>28188</t>
+          <t>29056</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>21878</t>
+          <t>22402</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>36566</t>
+          <t>36803</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,89%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>267556</t>
+          <t>268638</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>264000</t>
+          <t>265101</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>268861</t>
+          <t>270198</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,22 +12560,22 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>230948</t>
+          <t>236763</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>223451</t>
+          <t>229280</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>237043</t>
+          <t>243778</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -12585,7 +12585,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>498504</t>
+          <t>505401</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>490126</t>
+          <t>497654</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>504814</t>
+          <t>512055</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,81%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,22 +12755,22 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>12327</t>
+          <t>13412</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5838</t>
+          <t>6787</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27722</t>
+          <t>27435</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -12780,7 +12780,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>279061</t>
+          <t>94858</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>91829</t>
+          <t>79511</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>566868</t>
+          <t>112742</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>291388</t>
+          <t>108269</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>95265</t>
+          <t>93138</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>650464</t>
+          <t>131904</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>8,85%</t>
         </is>
       </c>
     </row>
@@ -12868,27 +12868,27 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>611952</t>
+          <t>706275</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>596557</t>
+          <t>692252</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>618441</t>
+          <t>712900</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>569557</t>
+          <t>676475</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>281750</t>
+          <t>658591</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>756789</t>
+          <t>691822</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>67,12%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1181509</t>
+          <t>1382751</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>822433</t>
+          <t>1359116</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1377632</t>
+          <t>1397882</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,75%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>848618</t>
+          <t>771333</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>848618</t>
+          <t>771333</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>848618</t>
+          <t>771333</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1472897</t>
+          <t>1491020</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1472897</t>
+          <t>1491020</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1472897</t>
+          <t>1491020</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>10159</t>
+          <t>11774</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3158</t>
+          <t>6255</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18500</t>
+          <t>19124</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>54555</t>
+          <t>58205</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>43570</t>
+          <t>45175</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>75828</t>
+          <t>71502</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>64714</t>
+          <t>69979</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>39318</t>
+          <t>57395</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>86310</t>
+          <t>84593</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>918561</t>
+          <t>786298</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>910220</t>
+          <t>778948</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>925562</t>
+          <t>791817</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>660296</t>
+          <t>771801</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>639023</t>
+          <t>758504</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>671281</t>
+          <t>784831</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1578858</t>
+          <t>1558099</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1557262</t>
+          <t>1543485</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1604254</t>
+          <t>1570683</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>96,47%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>714851</t>
+          <t>830006</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>714851</t>
+          <t>830006</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>714851</t>
+          <t>830006</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1643572</t>
+          <t>1628078</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1643572</t>
+          <t>1628078</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1643572</t>
+          <t>1628078</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>45124</t>
+          <t>47404</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>31327</t>
+          <t>34212</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>61801</t>
+          <t>63640</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>486253</t>
+          <t>311059</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>287815</t>
+          <t>283571</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1179965</t>
+          <t>344144</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>531377</t>
+          <t>358463</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>322547</t>
+          <t>327281</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1247335</t>
+          <t>389166</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3413696</t>
+          <t>3484371</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3397019</t>
+          <t>3468135</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3427493</t>
+          <t>3497563</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3170775</t>
+          <t>3420483</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2477063</t>
+          <t>3387398</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3369213</t>
+          <t>3447971</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6584471</t>
+          <t>6904853</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5868513</t>
+          <t>6874150</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6793301</t>
+          <t>6936035</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,49%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3458820</t>
+          <t>3531775</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3458820</t>
+          <t>3531775</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3458820</t>
+          <t>3531775</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3657028</t>
+          <t>3731542</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3657028</t>
+          <t>3731542</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3657028</t>
+          <t>3731542</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7115848</t>
+          <t>7263316</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7115848</t>
+          <t>7263316</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7115848</t>
+          <t>7263316</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
